--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103803</v>
+        <v>103878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,6 +896,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127301709</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backagruvan, Västmanland, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>482756</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6631597</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103878</v>
+        <v>103884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103884</v>
+        <v>103885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103885</v>
+        <v>103891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103891</v>
+        <v>103893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103893</v>
+        <v>103895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103895</v>
+        <v>103901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103901</v>
+        <v>103904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103904</v>
+        <v>103912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103912</v>
+        <v>103878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100558</v>
+        <v>100525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127071817</v>
       </c>
       <c r="B3" t="n">
-        <v>103878</v>
+        <v>103912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127301709</v>
       </c>
       <c r="B4" t="n">
-        <v>100525</v>
+        <v>100558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104518446</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482767.8513065206</v>
+        <v>482768</v>
       </c>
       <c r="R2" t="n">
-        <v>6631567.944843542</v>
+        <v>6631568</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127071817</v>
+        <v>104518443</v>
       </c>
       <c r="B3" t="n">
-        <v>103912</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backagruvan, Backagruvan, Vstm</t>
+          <t>Jönshyttan, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482812</v>
+        <v>482716</v>
       </c>
       <c r="R3" t="n">
-        <v>6631492</v>
+        <v>6631661</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,31 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127301709</v>
+        <v>104518447</v>
       </c>
       <c r="B4" t="n">
-        <v>100558</v>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -928,20 +898,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backagruvan, Västmanland, Vstm</t>
+          <t>Jönshyttan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482756</v>
+        <v>482780</v>
       </c>
       <c r="R4" t="n">
-        <v>6631597</v>
+        <v>6631535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,22 +948,332 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127071817</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Backagruvan, Backagruvan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>482812</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6631492</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104518484</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jönshyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>482831</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6631454</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127301709</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Backagruvan, Västmanland, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>482756</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6631597</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Anna Hammar</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Anna Hammar</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4652-2023 artfynd.xlsx
+++ b/artfynd/A 4652-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518446</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518443</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518447</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127071817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518484</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,8 +1304,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301709</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>